--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136480982</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136480983</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>136480984</v>
       </c>
       <c r="B5" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>136480953</v>
       </c>
       <c r="B6" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136480954</v>
       </c>
       <c r="B7" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37476-2026 artfynd.xlsx
+++ b/artfynd/A 37476-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136480982</v>
+        <v>136583114</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734455</v>
+        <v>734322</v>
       </c>
       <c r="R3" t="n">
-        <v>7266101</v>
+        <v>7265662</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:46</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -911,13 +901,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480982</t>
+          <t>https://artportalen.se/Sighting/136583114</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136480983</v>
+        <v>136480982</v>
       </c>
       <c r="B4" t="n">
         <v>80589</v>
@@ -956,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734596</v>
+        <v>734455</v>
       </c>
       <c r="R4" t="n">
-        <v>7266022</v>
+        <v>7266101</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1032,13 +1022,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480983</t>
+          <t>https://artportalen.se/Sighting/136480982</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136480984</v>
+        <v>136480983</v>
       </c>
       <c r="B5" t="n">
         <v>80589</v>
@@ -1077,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734669</v>
+        <v>734596</v>
       </c>
       <c r="R5" t="n">
-        <v>7265768</v>
+        <v>7266022</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,22 +1097,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,38 +1143,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480984</t>
+          <t>https://artportalen.se/Sighting/136480983</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136480953</v>
+        <v>136480984</v>
       </c>
       <c r="B6" t="n">
-        <v>80594</v>
+        <v>80589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1198,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734571</v>
+        <v>734669</v>
       </c>
       <c r="R6" t="n">
-        <v>7266074</v>
+        <v>7265768</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,22 +1218,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1274,13 +1264,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480953</t>
+          <t>https://artportalen.se/Sighting/136480984</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136480954</v>
+        <v>136480953</v>
       </c>
       <c r="B7" t="n">
         <v>80594</v>
@@ -1319,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734733</v>
+        <v>734571</v>
       </c>
       <c r="R7" t="n">
-        <v>7265704</v>
+        <v>7266074</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,22 +1339,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,16 +1385,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480954</t>
+          <t>https://artportalen.se/Sighting/136480953</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16747841</v>
+        <v>136480954</v>
       </c>
       <c r="B8" t="n">
-        <v>99017</v>
+        <v>80594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,37 +1402,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219795</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storljugaren, Nb</t>
+          <t>Risnabben, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734817</v>
+        <v>734733</v>
       </c>
       <c r="R8" t="n">
-        <v>7265484</v>
+        <v>7265704</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,12 +1460,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,36 +1491,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>grusvägs vändplan</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16747841</t>
+          <t>https://artportalen.se/Sighting/136480954</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16747840</v>
+        <v>16747841</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>99017</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,21 +1523,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1609,16 +1613,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16747840</t>
+          <t>https://artportalen.se/Sighting/16747841</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16747837</v>
+        <v>136583113</v>
       </c>
       <c r="B10" t="n">
-        <v>97974</v>
+        <v>98204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,34 +1630,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224360</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gul groddlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Huperzia arctica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Grossh. ex Tolm.) Sipliv.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storljugaren, Nb</t>
+          <t>Risnabben, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>734817</v>
+        <v>733774</v>
       </c>
       <c r="R10" t="n">
-        <v>7265484</v>
+        <v>7266009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,12 +1688,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-06-10</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,25 +1709,234 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>grusvägs vändplan</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136583113</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16747840</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storljugaren, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>734817</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7265484</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-06-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-06-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>grusvägs vändplan</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16747840</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16747837</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97974</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224360</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gul groddlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Huperzia arctica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Grossh. ex Tolm.) Sipliv.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storljugaren, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>734817</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7265484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-06-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-06-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>grusvägs vändplan</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Birgitta Öster</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16747837</t>
         </is>
@@ -1731,6 +1953,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
